--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,12 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -91,6 +97,9 @@
     <t>NAJERA</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>GALICIA</t>
   </si>
   <si>
@@ -98,6 +107,12 @@
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>ROGELIO</t>
@@ -875,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -913,10 +928,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -936,10 +951,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -953,16 +968,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920148</v>
+        <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -971,6 +986,52 @@
         <v>12</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920382</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920148</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -79,43 +79,28 @@
     <t>AVELLEIRA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
     <t>RONALDO</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
   </si>
 </sst>
 </file>
@@ -659,16 +644,19 @@
         <v>41</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>41</v>
       </c>
-      <c r="E2">
-        <v>41</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,16 +670,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.3</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -705,16 +696,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>90.23999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -728,16 +722,19 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -802,7 +799,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -819,16 +816,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -845,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>95.12</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -928,10 +925,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -945,16 +942,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920141</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -968,16 +965,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -987,52 +984,6 @@
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920382</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920148</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -82,25 +82,16 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>SOL</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -887,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,10 +916,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -948,10 +939,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -960,29 +951,6 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920382</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20222.xlsx
@@ -76,22 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>AVELLEIRA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>SOL</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
   </si>
 </sst>
 </file>
@@ -790,7 +790,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -807,16 +807,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>96.3</v>
+        <v>92.59</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,7 +868,7 @@
         <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +910,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920332</v>
+        <v>21330051920147</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -925,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920147</v>
+        <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -948,10 +948,10 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
